--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.90025569365781</v>
+        <v>3.883791550219394</v>
       </c>
       <c r="D2" t="n">
-        <v>29.29606966074785</v>
+        <v>4.760611319871526</v>
       </c>
       <c r="E2" t="n">
-        <v>14.53774743089852</v>
+        <v>2.362383957521009</v>
       </c>
       <c r="F2" t="n">
-        <v>18.64557689631305</v>
+        <v>3.029906245650871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.42307869337692</v>
+        <v>7.54375028767375</v>
       </c>
       <c r="D3" t="n">
-        <v>71.8387782514463</v>
+        <v>11.67380146586002</v>
       </c>
       <c r="E3" t="n">
-        <v>14.53774743089852</v>
+        <v>2.362383957521009</v>
       </c>
       <c r="F3" t="n">
-        <v>18.64557689631305</v>
+        <v>3.029906245650871</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.00575400955621</v>
+        <v>8.775935026552883</v>
       </c>
       <c r="D4" t="n">
-        <v>73.19672804687424</v>
+        <v>11.89446830761706</v>
       </c>
       <c r="E4" t="n">
-        <v>14.53774743089852</v>
+        <v>2.362383957521009</v>
       </c>
       <c r="F4" t="n">
-        <v>18.64557689631305</v>
+        <v>3.029906245650871</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.44747325639162</v>
+        <v>2.997714404163638</v>
       </c>
       <c r="D5" t="n">
-        <v>82.57549973091879</v>
+        <v>13.4185187062743</v>
       </c>
       <c r="E5" t="n">
-        <v>14.53774743089852</v>
+        <v>2.362383957521009</v>
       </c>
       <c r="F5" t="n">
-        <v>18.64557689631305</v>
+        <v>3.029906245650871</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.12697065101595</v>
+        <v>3.433132730790091</v>
       </c>
       <c r="D6" t="n">
-        <v>71.56290917724893</v>
+        <v>11.62897274130295</v>
       </c>
       <c r="E6" t="n">
-        <v>14.53774743089852</v>
+        <v>2.362383957521009</v>
       </c>
       <c r="F6" t="n">
-        <v>18.64557689631305</v>
+        <v>3.029906245650871</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
